--- a/Demo/lf/demo_lf_tas_9999_1_site.xlsx
+++ b/Demo/lf/demo_lf_tas_9999_1_site.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\lf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2577999E-4C4E-4E33-A0A4-B949D5690DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CE8019-9F6D-458C-A35D-640B7B6EDF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -727,10 +727,10 @@
     <t>${c_site}</t>
   </si>
   <si>
-    <t>demo_lf_tas_9999_1_site</t>
-  </si>
-  <si>
-    <t>(Demo) 1. TAS1 LF Site Form</t>
+    <t>demo_lf_tas_9999_1_site_v2</t>
+  </si>
+  <si>
+    <t>(Demo) 1. TAS1 LF Site Form V2</t>
   </si>
 </sst>
 </file>

--- a/Demo/lf/demo_lf_tas_9999_1_site.xlsx
+++ b/Demo/lf/demo_lf_tas_9999_1_site.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\lf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CE8019-9F6D-458C-A35D-640B7B6EDF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B73F7D7-A63F-4815-9516-51D005EB3112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -313,9 +313,6 @@
     <t>Enter the replacement school name</t>
   </si>
   <si>
-    <t>Select the ESPEN Collect school ID</t>
-  </si>
-  <si>
     <t>regex(., '^[0-9]{3}$')</t>
   </si>
   <si>
@@ -667,9 +664,6 @@
     <t>school = ${c_school_1}</t>
   </si>
   <si>
-    <t>${c_school_2} != 'Other'</t>
-  </si>
-  <si>
     <t>if(${c_school_1} = 'Other',concat( ${c_school_2}), concat(${c_school_1}))</t>
   </si>
   <si>
@@ -721,9 +715,6 @@
     <t>Site ID</t>
   </si>
   <si>
-    <t>{c_community}</t>
-  </si>
-  <si>
     <t>${c_site}</t>
   </si>
   <si>
@@ -731,6 +722,15 @@
   </si>
   <si>
     <t>(Demo) 1. TAS1 LF Site Form V2</t>
+  </si>
+  <si>
+    <t>Select the school ID</t>
+  </si>
+  <si>
+    <t>${c_school_1} != 'Other'</t>
+  </si>
+  <si>
+    <t>${c_community}</t>
   </si>
 </sst>
 </file>
@@ -1267,16 +1267,16 @@
         <v>84</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="S1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:19" s="4" customFormat="1" ht="47.25">
@@ -1330,7 +1330,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D4" s="5"/>
       <c r="G4" s="5"/>
@@ -1345,18 +1345,18 @@
         <v>88</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:19" s="4" customFormat="1">
       <c r="A5" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>119</v>
       </c>
       <c r="D5" s="5"/>
       <c r="G5" s="5"/>
@@ -1371,10 +1371,10 @@
         <v>20</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:19" s="4" customFormat="1">
@@ -1382,7 +1382,7 @@
         <v>89</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>90</v>
@@ -1397,7 +1397,7 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:19" s="4" customFormat="1">
@@ -1405,7 +1405,7 @@
         <v>34</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>91</v>
@@ -1413,7 +1413,7 @@
       <c r="D7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5" t="s">
@@ -1425,19 +1425,19 @@
     </row>
     <row r="8" spans="1:19" s="4" customFormat="1">
       <c r="A8" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>92</v>
+        <v>229</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
@@ -1446,29 +1446,29 @@
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:19" s="4" customFormat="1" ht="31.5">
       <c r="A9" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5" t="s">
@@ -1477,7 +1477,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:19" s="4" customFormat="1" ht="47.25">
@@ -1485,16 +1485,16 @@
         <v>34</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -1504,10 +1504,10 @@
         <v>17</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:19" s="4" customFormat="1" ht="47.25">
@@ -1515,16 +1515,16 @@
         <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -1534,10 +1534,10 @@
         <v>17</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:19" s="4" customFormat="1" ht="15.75" customHeight="1">
@@ -1583,10 +1583,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D14" s="5"/>
       <c r="H14" s="4" t="s">
@@ -1601,10 +1601,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D15" s="5"/>
       <c r="H15" s="4" t="s">
@@ -1619,10 +1619,10 @@
         <v>24</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="D16" s="5"/>
       <c r="H16" s="4" t="s">
@@ -1637,10 +1637,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>105</v>
       </c>
       <c r="D17" s="5"/>
       <c r="H17" s="4" t="s">
@@ -1655,10 +1655,10 @@
         <v>24</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D18" s="5"/>
       <c r="H18" s="4" t="s">
@@ -1673,10 +1673,10 @@
         <v>22</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>108</v>
       </c>
       <c r="D19" s="5"/>
       <c r="H19" s="4" t="s">
@@ -1799,16 +1799,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1">
@@ -1860,10 +1860,10 @@
         <v>64</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="4" customFormat="1">
@@ -1871,10 +1871,10 @@
         <v>64</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="4" customFormat="1">
@@ -1882,10 +1882,10 @@
         <v>64</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="4" customFormat="1">
@@ -1893,10 +1893,10 @@
         <v>64</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="4" customFormat="1">
@@ -1904,10 +1904,10 @@
         <v>64</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="4" customFormat="1">
@@ -1915,10 +1915,10 @@
         <v>64</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="4" customFormat="1">
@@ -1926,10 +1926,10 @@
         <v>64</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="4" customFormat="1">
@@ -1937,10 +1937,10 @@
         <v>64</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="4" customFormat="1">
@@ -1948,10 +1948,10 @@
         <v>64</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="4" customFormat="1">
@@ -1959,10 +1959,10 @@
         <v>64</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="4" customFormat="1">
@@ -1970,10 +1970,10 @@
         <v>64</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="4" customFormat="1">
@@ -2506,24 +2506,24 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2536,13 +2536,13 @@
         <v>41</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2550,13 +2550,13 @@
         <v>41</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2564,13 +2564,13 @@
         <v>41</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2578,13 +2578,13 @@
         <v>41</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2594,338 +2594,338 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2934,1010 +2934,1010 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -3946,7 +3946,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B170" s="12">
         <v>101</v>
@@ -3955,12 +3955,12 @@
         <v>101</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B171" s="12">
         <v>102</v>
@@ -3969,12 +3969,12 @@
         <v>102</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B172" s="12">
         <v>103</v>
@@ -3983,12 +3983,12 @@
         <v>103</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B173" s="12">
         <v>104</v>
@@ -3997,12 +3997,12 @@
         <v>104</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B174" s="12">
         <v>105</v>
@@ -4011,12 +4011,12 @@
         <v>105</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B175" s="12">
         <v>106</v>
@@ -4025,12 +4025,12 @@
         <v>106</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B176" s="12">
         <v>107</v>
@@ -4039,12 +4039,12 @@
         <v>107</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B177" s="12">
         <v>108</v>
@@ -4053,12 +4053,12 @@
         <v>108</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B178" s="12">
         <v>109</v>
@@ -4067,12 +4067,12 @@
         <v>109</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B179" s="12">
         <v>110</v>
@@ -4081,12 +4081,12 @@
         <v>110</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B180" s="12">
         <v>111</v>
@@ -4095,12 +4095,12 @@
         <v>111</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B181" s="12">
         <v>112</v>
@@ -4109,12 +4109,12 @@
         <v>112</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B182" s="12">
         <v>113</v>
@@ -4123,12 +4123,12 @@
         <v>113</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B183" s="12">
         <v>114</v>
@@ -4137,12 +4137,12 @@
         <v>114</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B184" s="12">
         <v>115</v>
@@ -4151,12 +4151,12 @@
         <v>115</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B185" s="12">
         <v>116</v>
@@ -4165,12 +4165,12 @@
         <v>116</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B186" s="12">
         <v>117</v>
@@ -4179,12 +4179,12 @@
         <v>117</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B187" s="12">
         <v>118</v>
@@ -4193,12 +4193,12 @@
         <v>118</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B188" s="12">
         <v>119</v>
@@ -4207,12 +4207,12 @@
         <v>119</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B189" s="12">
         <v>120</v>
@@ -4221,12 +4221,12 @@
         <v>120</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B190" s="12">
         <v>121</v>
@@ -4235,12 +4235,12 @@
         <v>121</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B191" s="12">
         <v>122</v>
@@ -4249,12 +4249,12 @@
         <v>122</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B192" s="12">
         <v>123</v>
@@ -4263,12 +4263,12 @@
         <v>123</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B193" s="12">
         <v>124</v>
@@ -4277,12 +4277,12 @@
         <v>124</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B194" s="12">
         <v>125</v>
@@ -4291,12 +4291,12 @@
         <v>125</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B195" s="12">
         <v>126</v>
@@ -4305,12 +4305,12 @@
         <v>126</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B196" s="12">
         <v>127</v>
@@ -4319,12 +4319,12 @@
         <v>127</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B197" s="12">
         <v>128</v>
@@ -4333,12 +4333,12 @@
         <v>128</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B198" s="12">
         <v>129</v>
@@ -4347,12 +4347,12 @@
         <v>129</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B199" s="12">
         <v>130</v>
@@ -4361,12 +4361,12 @@
         <v>130</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B200" s="12">
         <v>131</v>
@@ -4375,12 +4375,12 @@
         <v>131</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B201" s="12">
         <v>132</v>
@@ -4389,12 +4389,12 @@
         <v>132</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="202" spans="1:7">
       <c r="A202" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B202" s="12">
         <v>133</v>
@@ -4403,12 +4403,12 @@
         <v>133</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B203" s="12">
         <v>134</v>
@@ -4417,12 +4417,12 @@
         <v>134</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B204" s="12">
         <v>135</v>
@@ -4431,12 +4431,12 @@
         <v>135</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B205" s="12">
         <v>136</v>
@@ -4445,12 +4445,12 @@
         <v>136</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B206" s="12">
         <v>137</v>
@@ -4459,12 +4459,12 @@
         <v>137</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="207" spans="1:7">
       <c r="A207" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B207" s="12">
         <v>138</v>
@@ -4473,12 +4473,12 @@
         <v>138</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="208" spans="1:7">
       <c r="A208" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B208" s="12">
         <v>139</v>
@@ -4487,12 +4487,12 @@
         <v>139</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="209" spans="1:7">
       <c r="A209" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B209" s="12">
         <v>140</v>
@@ -4501,12 +4501,12 @@
         <v>140</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="210" spans="1:7">
       <c r="A210" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B210" s="12">
         <v>141</v>
@@ -4515,12 +4515,12 @@
         <v>141</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="211" spans="1:7">
       <c r="A211" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B211" s="12">
         <v>142</v>
@@ -4529,12 +4529,12 @@
         <v>142</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="212" spans="1:7">
       <c r="A212" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B212" s="12">
         <v>143</v>
@@ -4543,12 +4543,12 @@
         <v>143</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="213" spans="1:7">
       <c r="A213" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B213" s="12">
         <v>144</v>
@@ -4557,12 +4557,12 @@
         <v>144</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="214" spans="1:7">
       <c r="A214" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B214" s="12">
         <v>145</v>
@@ -4571,12 +4571,12 @@
         <v>145</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="215" spans="1:7">
       <c r="A215" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B215" s="12">
         <v>146</v>
@@ -4585,12 +4585,12 @@
         <v>146</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="216" spans="1:7">
       <c r="A216" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B216" s="12">
         <v>147</v>
@@ -4599,12 +4599,12 @@
         <v>147</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="217" spans="1:7">
       <c r="A217" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B217" s="12">
         <v>148</v>
@@ -4613,12 +4613,12 @@
         <v>148</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="219" spans="1:7">
       <c r="A219" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B219" s="12">
         <v>101</v>
@@ -4628,15 +4628,15 @@
         <v>LGEA ABADAWA II PRIMARY SCHOOL (101)</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="220" spans="1:7">
       <c r="A220" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B220" s="12">
         <v>102</v>
@@ -4646,15 +4646,15 @@
         <v>LGEA ABET PRIMARY SCHOOL (102)</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="221" spans="1:7">
       <c r="A221" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B221" s="12">
         <v>103</v>
@@ -4664,15 +4664,15 @@
         <v>ACHIDA DAN GALADIMA PRIMARY SCHOOL (103)</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="222" spans="1:7">
       <c r="A222" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B222" s="12">
         <v>104</v>
@@ -4682,15 +4682,15 @@
         <v>IHIYA US SUNNA ACHIDA (104)</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="223" spans="1:7">
       <c r="A223" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B223" s="12">
         <v>105</v>
@@ -4700,15 +4700,15 @@
         <v>LATE USMAN MAKERA MEMORIAL PRIMARY SCHOOL ACHIDA (105)</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="224" spans="1:7">
       <c r="A224" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B224" s="12">
         <v>106</v>
@@ -4718,15 +4718,15 @@
         <v>MADARASATUL ULUMULDDIN ISLAMIYYA MARNONA (106)</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="225" spans="1:7">
       <c r="A225" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B225" s="12">
         <v>107</v>
@@ -4736,15 +4736,15 @@
         <v>MALJAU SUNNAN ISLAMIYYA ACHIDA (107)</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="226" spans="1:7">
       <c r="A226" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B226" s="12">
         <v>108</v>
@@ -4754,15 +4754,15 @@
         <v>MUHAMMADU DANIYA ISLAMIYYAH SCHOOL ACHIDA (108)</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="227" spans="1:7">
       <c r="A227" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B227" s="12">
         <v>109</v>
@@ -4772,15 +4772,15 @@
         <v>SHEHU MAIGARI ISLAMIYYA SCHOOL (109)</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="228" spans="1:7">
       <c r="A228" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B228" s="12">
         <v>110</v>
@@ -4790,15 +4790,15 @@
         <v>SULTAN SA AD ABUBAKAR ISLAMIYA SCHOOL (110)</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="229" spans="1:7">
       <c r="A229" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B229" s="12">
         <v>111</v>
@@ -4808,15 +4808,15 @@
         <v>TAHZIBUL FITYANU ISLAMIYA ACHIDA (111)</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="230" spans="1:7">
       <c r="A230" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B230" s="12">
         <v>112</v>
@@ -4826,15 +4826,15 @@
         <v>ADAKANTA PRIMARY SCHOOL (112)</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="231" spans="1:7">
       <c r="A231" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B231" s="12">
         <v>113</v>
@@ -4844,15 +4844,15 @@
         <v>ADARAWA PRIMARY SCHOOL (113)</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="232" spans="1:7">
       <c r="A232" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B232" s="12">
         <v>114</v>
@@ -4862,15 +4862,15 @@
         <v>LGEA ADUWAN GIDA PRIMARY SCHOOL (114)</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="233" spans="1:7">
       <c r="A233" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B233" s="12">
         <v>115</v>
@@ -4880,15 +4880,15 @@
         <v>AJOGAL PRIMARY SCHOOL (115)</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="234" spans="1:7">
       <c r="A234" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B234" s="12">
         <v>116</v>
@@ -4898,15 +4898,15 @@
         <v>ALELA PRIMARY SCHOOL (AJOGAL) (116)</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="235" spans="1:7">
       <c r="A235" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B235" s="12">
         <v>117</v>
@@ -4916,15 +4916,15 @@
         <v>ALELA PRIMARY SCHOOL (117)</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="236" spans="1:7">
       <c r="A236" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B236" s="12">
         <v>118</v>
@@ -4934,15 +4934,15 @@
         <v>LGEA ALHAZAWA RICHIFA PRIMARY SCHOOL (118)</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="237" spans="1:7">
       <c r="A237" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B237" s="12">
         <v>119</v>
@@ -4952,15 +4952,15 @@
         <v>ALKAMMU MODEL PRIMARY SCHOOL (119)</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="238" spans="1:7">
       <c r="A238" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B238" s="12">
         <v>120</v>
@@ -4970,15 +4970,15 @@
         <v>ALKASU PRIMARY SCHOOL (120)</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="239" spans="1:7">
       <c r="A239" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B239" s="12">
         <v>121</v>
@@ -4988,15 +4988,15 @@
         <v>SANI DINGYADI PRIMARY SCHOOL AMANAWA (121)</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="240" spans="1:7">
       <c r="A240" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B240" s="12">
         <v>122</v>
@@ -5006,15 +5006,15 @@
         <v>UBE ANCHAU GARI PRIMARY SCHOOL (CENTRAL P/S) (122)</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="241" spans="1:7">
       <c r="A241" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B241" s="12">
         <v>123</v>
@@ -5024,15 +5024,15 @@
         <v>LGEA UMARU SALANKE ANCHAU - TAKALAFIYA PRIMARY SCHOOL (123)</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="242" spans="1:7">
       <c r="A242" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B242" s="12">
         <v>124</v>
@@ -5042,15 +5042,15 @@
         <v>NYSC ANCHAU TAKALAFIYA PRIMARY SCHOOL (UBE FADA ANCHAU TAKALAFIYA) (124)</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="243" spans="1:7">
       <c r="A243" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B243" s="12">
         <v>125</v>
@@ -5060,15 +5060,15 @@
         <v>LGEA ANCHUNA SARKI PRIMARY SCHOOL (125)</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B244" s="12">
         <v>126</v>
@@ -5078,15 +5078,15 @@
         <v>UBE UNGWAN KANAWA ZUNTU PRIMARY SCHOOL (126)</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="245" spans="1:7">
       <c r="A245" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B245" s="12">
         <v>127</v>
@@ -5096,15 +5096,15 @@
         <v>EVAHJOSHUA ACADEMY ANGUWAN FULANI PALLADAN (127)</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="246" spans="1:7">
       <c r="A246" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B246" s="12">
         <v>128</v>
@@ -5114,15 +5114,15 @@
         <v>LGEA ANGUWAN BISO VILLAGE PRIMARY SCHOOL (128)</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="247" spans="1:7">
       <c r="A247" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B247" s="12">
         <v>129</v>
@@ -5132,15 +5132,15 @@
         <v>UBE ANGUWAN DAWA PRIMARY SCHOOL (129)</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="248" spans="1:7">
       <c r="A248" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B248" s="12">
         <v>130</v>
@@ -5150,15 +5150,15 @@
         <v>ARMY CHILDREN SCHOOL SABON GARI (130)</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="249" spans="1:7">
       <c r="A249" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B249" s="12">
         <v>131</v>
@@ -5168,15 +5168,15 @@
         <v>LGEA UNGWAN KANAWA PRIMARY SCHOOL (131)</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="250" spans="1:7">
       <c r="A250" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B250" s="12">
         <v>132</v>
@@ -5186,15 +5186,15 @@
         <v>UBE UNGWAN LIMAN SUDDU PRIMARY SCHOOL (132)</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="251" spans="1:7">
       <c r="A251" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B251" s="12">
         <v>133</v>
@@ -5204,15 +5204,15 @@
         <v>UBE ANG. MAJE PRIMARY SCHOOL (133)</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="252" spans="1:7">
       <c r="A252" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B252" s="12">
         <v>134</v>
@@ -5222,15 +5222,15 @@
         <v>UBE ANGUWAN MALAM SAMBO PRIMARY SCHOOL (134)</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="253" spans="1:7">
       <c r="A253" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B253" s="12">
         <v>135</v>
@@ -5240,15 +5240,15 @@
         <v>LGEA UNGWAN SARKIN YAKI KUBAU PRIMARY SCHOOL (135)</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="254" spans="1:7">
       <c r="A254" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B254" s="12">
         <v>136</v>
@@ -5258,15 +5258,15 @@
         <v>GREAT APEX AMAZING SCHOOL (136)</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="255" spans="1:7">
       <c r="A255" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B255" s="12">
         <v>137</v>
@@ -5276,15 +5276,15 @@
         <v>AL FALAAH INTERNATIONAL ACADEMY (137)</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="256" spans="1:7">
       <c r="A256" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B256" s="12">
         <v>138</v>
@@ -5294,15 +5294,15 @@
         <v>ZENITH SCIENCE ACADEMY (138)</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="257" spans="1:7">
       <c r="A257" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B257" s="12">
         <v>139</v>
@@ -5312,15 +5312,15 @@
         <v>LGEA ANTANG GIDA PRIMARY SCHOOL (139)</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="258" spans="1:7">
       <c r="A258" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B258" s="12">
         <v>140</v>
@@ -5330,15 +5330,15 @@
         <v>UBE APIOJYIM PRIMARY SCHOOL (140)</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="259" spans="1:7">
       <c r="A259" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B259" s="12">
         <v>141</v>
@@ -5348,15 +5348,15 @@
         <v>ARABA PRIMARY SCHOOL (141)</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="260" spans="1:7">
       <c r="A260" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B260" s="12">
         <v>142</v>
@@ -5366,15 +5366,15 @@
         <v>ARABA DAJI PRIMARY SCHOOL (142)</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="261" spans="1:7">
       <c r="A261" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B261" s="12">
         <v>143</v>
@@ -5384,15 +5384,15 @@
         <v>ARBA PRIMARY SCHOOL (143)</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="262" spans="1:7">
       <c r="A262" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B262" s="12">
         <v>144</v>
@@ -5402,15 +5402,15 @@
         <v>LGEA ASHAFA GIDA PRIMARY SCHOOL (144)</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="263" spans="1:7">
       <c r="A263" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B263" s="12">
         <v>145</v>
@@ -5420,15 +5420,15 @@
         <v>SAUDAT ABUBAKAR MEMORIAL ARABIC &amp; ISLAMIC SCHOOL (145)</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="264" spans="1:7">
       <c r="A264" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B264" s="12">
         <v>146</v>
@@ -5438,15 +5438,15 @@
         <v>AYAMA PRIMARY SCHOOL (146)</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="265" spans="1:7">
       <c r="A265" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B265" s="12">
         <v>147</v>
@@ -5456,15 +5456,15 @@
         <v>LGEA BABAN FADAMA PRIMARY SCHOOL (147)</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="266" spans="1:7">
       <c r="A266" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B266" s="12">
         <v>148</v>
@@ -5474,10 +5474,10 @@
         <v>LGEA BAGALDI PRIMARY SCHOOL (148)</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -5520,10 +5520,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>49</v>
